--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,6 +1250,230 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129886396</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106653</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tofta-Visby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>691940</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6384182</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129885895</v>
+      </c>
+      <c r="B8" t="n">
+        <v>44858</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tofta-Visby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>691925</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6384183</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera på åkervädd</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>129886396</v>
       </c>
       <c r="B7" t="n">
-        <v>106653</v>
+        <v>106663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>129886396</v>
       </c>
       <c r="B7" t="n">
-        <v>106663</v>
+        <v>106667</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>129886396</v>
       </c>
       <c r="B7" t="n">
-        <v>106667</v>
+        <v>106670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129885895</v>
       </c>
       <c r="B8" t="n">
-        <v>44858</v>
+        <v>44861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>129886396</v>
       </c>
       <c r="B7" t="n">
-        <v>106670</v>
+        <v>106671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>129886396</v>
       </c>
       <c r="B7" t="n">
-        <v>106671</v>
+        <v>106688</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>129886396</v>
       </c>
       <c r="B7" t="n">
-        <v>106704</v>
+        <v>106707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>129886396</v>
       </c>
       <c r="B7" t="n">
-        <v>106707</v>
+        <v>106794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129885895</v>
       </c>
       <c r="B8" t="n">
-        <v>44862</v>
+        <v>44947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129886396</v>
+        <v>131599789</v>
       </c>
       <c r="B7" t="n">
-        <v>106707</v>
+        <v>106972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1297,7 +1297,7 @@
         <v>6384182</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,19 +1324,9 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129885895</v>
+        <v>131598634</v>
       </c>
       <c r="B8" t="n">
-        <v>44862</v>
+        <v>44996</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1385,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1405,7 +1395,7 @@
         <v>6384183</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,19 +1422,9 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>131599789</v>
       </c>
       <c r="B7" t="n">
-        <v>106972</v>
+        <v>106974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>131599789</v>
       </c>
       <c r="B7" t="n">
-        <v>106974</v>
+        <v>106975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>131599789</v>
       </c>
       <c r="B7" t="n">
-        <v>106975</v>
+        <v>106976</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131598634</v>
       </c>
       <c r="B8" t="n">
-        <v>44996</v>
+        <v>44997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>131599789</v>
       </c>
       <c r="B7" t="n">
-        <v>106976</v>
+        <v>106974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131598634</v>
       </c>
       <c r="B8" t="n">
-        <v>44997</v>
+        <v>45000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>131599789</v>
       </c>
       <c r="B7" t="n">
-        <v>106975</v>
+        <v>106981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>131599789</v>
       </c>
       <c r="B7" t="n">
-        <v>106981</v>
+        <v>106987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131598634</v>
       </c>
       <c r="B8" t="n">
-        <v>45000</v>
+        <v>45001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>131599789</v>
       </c>
       <c r="B7" t="n">
-        <v>106987</v>
+        <v>106992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131598634</v>
       </c>
       <c r="B8" t="n">
-        <v>45001</v>
+        <v>45004</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88771541</v>
+        <v>131598560</v>
       </c>
       <c r="B2" t="n">
-        <v>85244</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6037417</v>
+        <v>671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulfotad denisespindling</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>A.Ortega, Vila &amp; Fern.-Brime</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenkumla källgårds, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691918.9899461782</v>
+        <v>692010</v>
       </c>
       <c r="R2" t="n">
-        <v>6384142.873503712</v>
+        <v>6384184</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sparsam</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,81 +759,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Sofie Alveteg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Mikael Molander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88771540</v>
+        <v>134263232</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkumla källgårds, Gtl</t>
+          <t>Stenkumla Backskogen, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691917.0167547583</v>
+        <v>692011</v>
       </c>
       <c r="R3" t="n">
-        <v>6384070.781010938</v>
+        <v>6384184</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,24 +840,24 @@
           <t>Stenkumla</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>I-Got-4456</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sparsam</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,61 +866,59 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112949109</v>
+        <v>88771548</v>
       </c>
       <c r="B4" t="n">
-        <v>89805</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>2072</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -964,14 +928,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Schills hage Stenkumla, Gtl</t>
+          <t>Stenkumla källgårds, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691827</v>
+        <v>692064</v>
       </c>
       <c r="R4" t="n">
-        <v>6384111</v>
+        <v>6384090</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2020-10-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2020-10-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,42 +994,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112949108</v>
+        <v>112949109</v>
       </c>
       <c r="B5" t="n">
-        <v>85888</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691826</v>
+        <v>691827</v>
       </c>
       <c r="R5" t="n">
-        <v>6384137</v>
+        <v>6384111</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,12 +1103,7 @@
         <v>112949107</v>
       </c>
       <c r="B6" t="n">
-        <v>85851</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,52 +1206,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131599789</v>
+        <v>112949115</v>
       </c>
       <c r="B7" t="n">
-        <v>106995</v>
+        <v>87309</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221903</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gotland (västra), Gtl</t>
+          <t>Schills hage Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691940</v>
+        <v>691812</v>
       </c>
       <c r="R7" t="n">
-        <v>6384182</v>
+        <v>6384092</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,12 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,67 +1294,75 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofie Alveteg</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hanna Bengtsson</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131598634</v>
+        <v>112949113</v>
       </c>
       <c r="B8" t="n">
-        <v>45005</v>
+        <v>87146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102018</v>
+        <v>3762</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gotland (västra), Gtl</t>
+          <t>Schills hage Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691925</v>
+        <v>691812</v>
       </c>
       <c r="R8" t="n">
-        <v>6384183</v>
+        <v>6384092</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,17 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera på åkervädd</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,15 +1406,646 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>88771540</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stenkumla källgårds, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>691917</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6384071</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-10-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-10-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>88771547</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stenkumla källgårds, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>692064</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6384090</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-10-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-10-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131598634</v>
+      </c>
+      <c r="B11" t="n">
+        <v>45050</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>691925</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6384183</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera på åkervädd</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Sofie Alveteg</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Mikael Molander</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131599789</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107142</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>691940</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6384182</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112949108</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Schills hage Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>691826</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6384137</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>88771541</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stenkumla källgårds, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>691919</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6384143</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-10-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-10-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44944-2022 artfynd.xlsx
+++ b/artfynd/A 44944-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112949109</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112949107</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112949115</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112949113</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112949108</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598560</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263232</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,6 +1561,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88771548</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1628,6 +1673,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88771540</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1735,6 +1785,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88771547</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598634</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1939,6 +1999,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599789</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2046,8 +2111,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88771541</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>